--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/102.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/102.xlsx
@@ -426,13 +426,13 @@
         <v>10.93933527553283</v>
       </c>
       <c r="E2">
-        <v>-12.3454509323604</v>
+        <v>-9.159085294817315</v>
       </c>
       <c r="F2">
-        <v>-5.42974220911497</v>
+        <v>-6.212899804171887</v>
       </c>
       <c r="G2">
-        <v>-5.522094623447247</v>
+        <v>-5.103049818090562</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>10.06601468906725</v>
       </c>
       <c r="E3">
-        <v>-12.73610427110609</v>
+        <v>-11.77254462870201</v>
       </c>
       <c r="F3">
-        <v>-5.470297420421228</v>
+        <v>-6.178029678351042</v>
       </c>
       <c r="G3">
-        <v>-6.473980279063718</v>
+        <v>-5.672912691205563</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>9.220605406387232</v>
       </c>
       <c r="E4">
-        <v>-13.91463057465429</v>
+        <v>-13.47082653648057</v>
       </c>
       <c r="F4">
-        <v>-5.555446134122392</v>
+        <v>-5.956922679563201</v>
       </c>
       <c r="G4">
-        <v>-6.855835719265656</v>
+        <v>-6.223882290581282</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>8.528892057111275</v>
       </c>
       <c r="E5">
-        <v>-13.87272407618731</v>
+        <v>-12.01721807933644</v>
       </c>
       <c r="F5">
-        <v>-5.326109305187738</v>
+        <v>-6.340667192379683</v>
       </c>
       <c r="G5">
-        <v>-6.496623989045446</v>
+        <v>-6.725981376050632</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>8.011828326442563</v>
       </c>
       <c r="E6">
-        <v>-15.10316480575943</v>
+        <v>-14.32144603713335</v>
       </c>
       <c r="F6">
-        <v>-5.358048667137479</v>
+        <v>-5.617088266034314</v>
       </c>
       <c r="G6">
-        <v>-6.088170966882648</v>
+        <v>-6.514473834328825</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>7.719389774259829</v>
       </c>
       <c r="E7">
-        <v>-15.11708533485901</v>
+        <v>-12.78430987691774</v>
       </c>
       <c r="F7">
-        <v>-5.035989361337864</v>
+        <v>-6.063391913477618</v>
       </c>
       <c r="G7">
-        <v>-6.225158685767906</v>
+        <v>-6.202895597487074</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>7.642314446684377</v>
       </c>
       <c r="E8">
-        <v>-15.93089739877745</v>
+        <v>-14.94830910859314</v>
       </c>
       <c r="F8">
-        <v>-5.110630234534517</v>
+        <v>-5.920536641395232</v>
       </c>
       <c r="G8">
-        <v>-6.516915063169052</v>
+        <v>-6.560597965789939</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>7.803774158706914</v>
       </c>
       <c r="E9">
-        <v>-16.33720114369365</v>
+        <v>-16.44955711229796</v>
       </c>
       <c r="F9">
-        <v>-5.257147718904679</v>
+        <v>-6.301894627724249</v>
       </c>
       <c r="G9">
-        <v>-6.037246408280067</v>
+        <v>-5.671032551252002</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>8.170826354426454</v>
       </c>
       <c r="E10">
-        <v>-17.54337830953268</v>
+        <v>-15.78044790682062</v>
       </c>
       <c r="F10">
-        <v>-5.085130600774139</v>
+        <v>-5.737640574163726</v>
       </c>
       <c r="G10">
-        <v>-5.810189157588052</v>
+        <v>-5.590803402902019</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>8.719844318801206</v>
       </c>
       <c r="E11">
-        <v>-18.31788774753855</v>
+        <v>-15.73647189573213</v>
       </c>
       <c r="F11">
-        <v>-5.009864310188373</v>
+        <v>-5.234870434341192</v>
       </c>
       <c r="G11">
-        <v>-6.14052285686359</v>
+        <v>-5.466008703331658</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>9.411573705881358</v>
       </c>
       <c r="E12">
-        <v>-18.10593252160954</v>
+        <v>-17.5072546723735</v>
       </c>
       <c r="F12">
-        <v>-5.243969221893542</v>
+        <v>-5.482254075513236</v>
       </c>
       <c r="G12">
-        <v>-5.270556178700215</v>
+        <v>-5.428231999517771</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>10.17900246444815</v>
       </c>
       <c r="E13">
-        <v>-19.10454255283299</v>
+        <v>-17.84568564886273</v>
       </c>
       <c r="F13">
-        <v>-4.915963894876633</v>
+        <v>-5.049316964481505</v>
       </c>
       <c r="G13">
-        <v>-5.213111832859016</v>
+        <v>-4.435947944061416</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>10.98618006506077</v>
       </c>
       <c r="E14">
-        <v>-20.43694640316183</v>
+        <v>-18.24761941636153</v>
       </c>
       <c r="F14">
-        <v>-4.701680986753054</v>
+        <v>-4.889918366997811</v>
       </c>
       <c r="G14">
-        <v>-4.964496956521449</v>
+        <v>-3.882766801354631</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>11.76644785541201</v>
       </c>
       <c r="E15">
-        <v>-21.4601279343509</v>
+        <v>-19.67282075605554</v>
       </c>
       <c r="F15">
-        <v>-4.392468831003457</v>
+        <v>-5.273124441002473</v>
       </c>
       <c r="G15">
-        <v>-4.317699281502147</v>
+        <v>-4.313476349355142</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>12.48224148726891</v>
       </c>
       <c r="E16">
-        <v>-22.21048702047386</v>
+        <v>-20.52556411101793</v>
       </c>
       <c r="F16">
-        <v>-4.093287376134359</v>
+        <v>-4.554190170684602</v>
       </c>
       <c r="G16">
-        <v>-3.588936691927917</v>
+        <v>-4.312252453713469</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>13.09801848056771</v>
       </c>
       <c r="E17">
-        <v>-23.09881059571451</v>
+        <v>-21.26621414886844</v>
       </c>
       <c r="F17">
-        <v>-4.063062734708414</v>
+        <v>-4.370908912610794</v>
       </c>
       <c r="G17">
-        <v>-4.00065781076392</v>
+        <v>-3.729878282792305</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>13.57519716760121</v>
       </c>
       <c r="E18">
-        <v>-23.36306969643211</v>
+        <v>-21.78627316085732</v>
       </c>
       <c r="F18">
-        <v>-3.879053341687546</v>
+        <v>-4.064515691132924</v>
       </c>
       <c r="G18">
-        <v>-3.430778531541122</v>
+        <v>-3.364698010555465</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>13.9089435509771</v>
       </c>
       <c r="E19">
-        <v>-24.28885280866421</v>
+        <v>-24.35395415099848</v>
       </c>
       <c r="F19">
-        <v>-3.309162247950973</v>
+        <v>-4.110513276275575</v>
       </c>
       <c r="G19">
-        <v>-3.662491835625989</v>
+        <v>-3.04019832321262</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>14.07671136413305</v>
       </c>
       <c r="E20">
-        <v>-26.2486948466518</v>
+        <v>-24.620527301934</v>
       </c>
       <c r="F20">
-        <v>-3.072138997885742</v>
+        <v>-3.288866418214982</v>
       </c>
       <c r="G20">
-        <v>-3.65362269375081</v>
+        <v>-3.606422321618198</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>14.08862714432977</v>
       </c>
       <c r="E21">
-        <v>-26.40695142779786</v>
+        <v>-25.92452856328673</v>
       </c>
       <c r="F21">
-        <v>-2.452094399746673</v>
+        <v>-3.617263563013415</v>
       </c>
       <c r="G21">
-        <v>-3.07299741392083</v>
+        <v>-3.48556508791917</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>13.9543733638969</v>
       </c>
       <c r="E22">
-        <v>-26.27165420987069</v>
+        <v>-24.304077538278</v>
       </c>
       <c r="F22">
-        <v>-2.438485980053482</v>
+        <v>-2.911966705247832</v>
       </c>
       <c r="G22">
-        <v>-3.474116905898267</v>
+        <v>-3.831638807015364</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>13.68538323237343</v>
       </c>
       <c r="E23">
-        <v>-26.93373975216213</v>
+        <v>-26.69041578678199</v>
       </c>
       <c r="F23">
-        <v>-2.255354656479582</v>
+        <v>-2.384439977225231</v>
       </c>
       <c r="G23">
-        <v>-3.966966227791542</v>
+        <v>-2.846035318654038</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>13.3208560547973</v>
       </c>
       <c r="E24">
-        <v>-27.78555929842695</v>
+        <v>-25.87805736302001</v>
       </c>
       <c r="F24">
-        <v>-1.877977803888419</v>
+        <v>-2.921518609769513</v>
       </c>
       <c r="G24">
-        <v>-4.672727454234066</v>
+        <v>-3.727040026143385</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>12.87447793562251</v>
       </c>
       <c r="E25">
-        <v>-27.56426635909412</v>
+        <v>-24.58548597006265</v>
       </c>
       <c r="F25">
-        <v>-1.831145224403746</v>
+        <v>-2.717022034142608</v>
       </c>
       <c r="G25">
-        <v>-3.852202222528404</v>
+        <v>-3.936047277036895</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>12.39402671407398</v>
       </c>
       <c r="E26">
-        <v>-28.04354646264393</v>
+        <v>-27.79973795054497</v>
       </c>
       <c r="F26">
-        <v>-1.18459204100769</v>
+        <v>-2.09538282875315</v>
       </c>
       <c r="G26">
-        <v>-4.18673588540003</v>
+        <v>-3.661937309182443</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>11.91217861087277</v>
       </c>
       <c r="E27">
-        <v>-27.95215732869514</v>
+        <v>-25.96014501135705</v>
       </c>
       <c r="F27">
-        <v>-1.506686966605625</v>
+        <v>-1.393156728949744</v>
       </c>
       <c r="G27">
-        <v>-3.831261466536028</v>
+        <v>-4.439278383944252</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>11.45878643499951</v>
       </c>
       <c r="E28">
-        <v>-27.8378994010076</v>
+        <v>-28.45875771593322</v>
       </c>
       <c r="F28">
-        <v>-1.93512769937496</v>
+        <v>-1.659900144692616</v>
       </c>
       <c r="G28">
-        <v>-4.436938872972369</v>
+        <v>-3.906171754738151</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>11.0816652203186</v>
       </c>
       <c r="E29">
-        <v>-26.82148793846</v>
+        <v>-26.08157604187273</v>
       </c>
       <c r="F29">
-        <v>-1.522099570502113</v>
+        <v>-1.736159647794338</v>
       </c>
       <c r="G29">
-        <v>-5.00018352220197</v>
+        <v>-3.62980758767236</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>10.78825631746867</v>
       </c>
       <c r="E30">
-        <v>-26.76254079230216</v>
+        <v>-25.05123499327754</v>
       </c>
       <c r="F30">
-        <v>-1.813429759127476</v>
+        <v>-2.056950723100266</v>
       </c>
       <c r="G30">
-        <v>-4.941200283449391</v>
+        <v>-5.363007877359129</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>10.61769764573873</v>
       </c>
       <c r="E31">
-        <v>-27.0997943655494</v>
+        <v>-26.10305459409112</v>
       </c>
       <c r="F31">
-        <v>-1.5017971138269</v>
+        <v>-2.283929190039151</v>
       </c>
       <c r="G31">
-        <v>-3.998449548654414</v>
+        <v>-4.577992025369777</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>10.57379794581068</v>
       </c>
       <c r="E32">
-        <v>-26.33038398927617</v>
+        <v>-25.92960498264932</v>
       </c>
       <c r="F32">
-        <v>-1.938238218972472</v>
+        <v>-1.958027916225352</v>
       </c>
       <c r="G32">
-        <v>-4.4654723756533</v>
+        <v>-4.72387513590269</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>10.65506403452284</v>
       </c>
       <c r="E33">
-        <v>-25.03219276007528</v>
+        <v>-24.45302357686428</v>
       </c>
       <c r="F33">
-        <v>-1.545351843498695</v>
+        <v>-2.253502426966922</v>
       </c>
       <c r="G33">
-        <v>-4.466522366552322</v>
+        <v>-5.431359003663922</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>10.86557646155617</v>
       </c>
       <c r="E34">
-        <v>-25.28143544098345</v>
+        <v>-24.48597275374409</v>
       </c>
       <c r="F34">
-        <v>-1.678588113299773</v>
+        <v>-2.546648396939222</v>
       </c>
       <c r="G34">
-        <v>-4.569136008380837</v>
+        <v>-3.543212869497054</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>11.1656943217339</v>
       </c>
       <c r="E35">
-        <v>-24.71868197605026</v>
+        <v>-23.24939594189157</v>
       </c>
       <c r="F35">
-        <v>-1.891034530891345</v>
+        <v>-2.104150269344379</v>
       </c>
       <c r="G35">
-        <v>-4.582559485780525</v>
+        <v>-3.698217775965223</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>11.54713462174023</v>
       </c>
       <c r="E36">
-        <v>-24.43217448253297</v>
+        <v>-22.3512591634763</v>
       </c>
       <c r="F36">
-        <v>-2.049927824259332</v>
+        <v>-2.156416110624015</v>
       </c>
       <c r="G36">
-        <v>-4.553793016368873</v>
+        <v>-5.024507217622133</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>11.96548884620489</v>
       </c>
       <c r="E37">
-        <v>-23.82789491094944</v>
+        <v>-22.86889997034508</v>
       </c>
       <c r="F37">
-        <v>-1.984006346344548</v>
+        <v>-2.168413355718759</v>
       </c>
       <c r="G37">
-        <v>-4.706172945589485</v>
+        <v>-5.198713832656172</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>12.38686328494692</v>
       </c>
       <c r="E38">
-        <v>-22.95265409711695</v>
+        <v>-20.52924123191216</v>
       </c>
       <c r="F38">
-        <v>-2.178034014734873</v>
+        <v>-2.886460444548232</v>
       </c>
       <c r="G38">
-        <v>-5.072518051479928</v>
+        <v>-4.963916180305428</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>12.79037012805421</v>
       </c>
       <c r="E39">
-        <v>-24.03753608666053</v>
+        <v>-21.38572510640487</v>
       </c>
       <c r="F39">
-        <v>-1.883150958318902</v>
+        <v>-3.140796573331973</v>
       </c>
       <c r="G39">
-        <v>-4.863766735868056</v>
+        <v>-4.862172062190166</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>13.13555148419143</v>
       </c>
       <c r="E40">
-        <v>-22.67025392952462</v>
+        <v>-21.04500272206775</v>
       </c>
       <c r="F40">
-        <v>-2.304644173680958</v>
+        <v>-2.757573931979255</v>
       </c>
       <c r="G40">
-        <v>-4.021847939594815</v>
+        <v>-3.154814673505583</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>13.42479472034762</v>
       </c>
       <c r="E41">
-        <v>-22.54190791919922</v>
+        <v>-19.97763686998584</v>
       </c>
       <c r="F41">
-        <v>-2.411415761697397</v>
+        <v>-2.581371073362369</v>
       </c>
       <c r="G41">
-        <v>-3.949598722077401</v>
+        <v>-4.761668245824374</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>13.63667854880821</v>
       </c>
       <c r="E42">
-        <v>-20.4732421223333</v>
+        <v>-18.96588520719213</v>
       </c>
       <c r="F42">
-        <v>-2.311701035585407</v>
+        <v>-3.080013458416754</v>
       </c>
       <c r="G42">
-        <v>-3.787535908034867</v>
+        <v>-4.781627916570477</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>13.7722170459331</v>
       </c>
       <c r="E43">
-        <v>-20.30410814662082</v>
+        <v>-17.47827243872441</v>
       </c>
       <c r="F43">
-        <v>-2.546014695876081</v>
+        <v>-2.595980989245544</v>
       </c>
       <c r="G43">
-        <v>-4.065642403748723</v>
+        <v>-5.154190937316067</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>13.84019456137652</v>
       </c>
       <c r="E44">
-        <v>-20.28668710711332</v>
+        <v>-18.06545702092898</v>
       </c>
       <c r="F44">
-        <v>-2.35245008486392</v>
+        <v>-2.93829801988062</v>
       </c>
       <c r="G44">
-        <v>-3.873599068317543</v>
+        <v>-4.56420761359855</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>13.831621197221</v>
       </c>
       <c r="E45">
-        <v>-18.35053351665985</v>
+        <v>-17.94269009058104</v>
       </c>
       <c r="F45">
-        <v>-2.438176170644835</v>
+        <v>-2.431255160994445</v>
       </c>
       <c r="G45">
-        <v>-4.236190456743981</v>
+        <v>-4.69385852107689</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>13.77199954685457</v>
       </c>
       <c r="E46">
-        <v>-19.01509160575948</v>
+        <v>-15.88604739220548</v>
       </c>
       <c r="F46">
-        <v>-2.132504457174804</v>
+        <v>-2.641353156999081</v>
       </c>
       <c r="G46">
-        <v>-4.422081501751203</v>
+        <v>-4.434533737569295</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>13.65478177554137</v>
       </c>
       <c r="E47">
-        <v>-17.78844573740578</v>
+        <v>-16.31132544321382</v>
       </c>
       <c r="F47">
-        <v>-2.307064663231938</v>
+        <v>-2.460788944006456</v>
       </c>
       <c r="G47">
-        <v>-4.230392538248442</v>
+        <v>-3.063606557817699</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>13.49265801433673</v>
       </c>
       <c r="E48">
-        <v>-17.02600015415634</v>
+        <v>-14.71890567231257</v>
       </c>
       <c r="F48">
-        <v>-2.149245762385382</v>
+        <v>-2.759802240292785</v>
       </c>
       <c r="G48">
-        <v>-4.100062417907298</v>
+        <v>-3.448434784752494</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>13.2943488932475</v>
       </c>
       <c r="E49">
-        <v>-16.04717955434641</v>
+        <v>-13.96484229445134</v>
       </c>
       <c r="F49">
-        <v>-2.406486147283338</v>
+        <v>-2.953741273371011</v>
       </c>
       <c r="G49">
-        <v>-4.066889267941312</v>
+        <v>-3.429656353767792</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>13.05245594299416</v>
       </c>
       <c r="E50">
-        <v>-15.47624313688136</v>
+        <v>-12.07064048720492</v>
       </c>
       <c r="F50">
-        <v>-2.693485631126865</v>
+        <v>-2.437225204866421</v>
       </c>
       <c r="G50">
-        <v>-4.557763294455802</v>
+        <v>-4.82456270067581</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>12.78989649596203</v>
       </c>
       <c r="E51">
-        <v>-14.46640249011888</v>
+        <v>-10.56766713490318</v>
       </c>
       <c r="F51">
-        <v>-2.334269077107276</v>
+        <v>-2.748714542606314</v>
       </c>
       <c r="G51">
-        <v>-3.824164184302949</v>
+        <v>-4.177732213440914</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>12.49626804988811</v>
       </c>
       <c r="E52">
-        <v>-13.28380508843779</v>
+        <v>-12.39753291192262</v>
       </c>
       <c r="F52">
-        <v>-2.634390728978552</v>
+        <v>-2.750684400290171</v>
       </c>
       <c r="G52">
-        <v>-3.93442307236497</v>
+        <v>-5.305015567517503</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>12.18627636560909</v>
       </c>
       <c r="E53">
-        <v>-13.22270238865229</v>
+        <v>-10.36000943080745</v>
       </c>
       <c r="F53">
-        <v>-2.146467418116392</v>
+        <v>-2.536832243216048</v>
       </c>
       <c r="G53">
-        <v>-4.300321932123328</v>
+        <v>-5.238879265765335</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>11.86441714198367</v>
       </c>
       <c r="E54">
-        <v>-13.23275560094932</v>
+        <v>-11.07104777712181</v>
       </c>
       <c r="F54">
-        <v>-2.160996153994093</v>
+        <v>-3.083244919655075</v>
       </c>
       <c r="G54">
-        <v>-5.154122031663319</v>
+        <v>-5.11954451886989</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>11.52453509606757</v>
       </c>
       <c r="E55">
-        <v>-11.29223203307845</v>
+        <v>-12.80933422428413</v>
       </c>
       <c r="F55">
-        <v>-1.758418708274964</v>
+        <v>-2.77644496978243</v>
       </c>
       <c r="G55">
-        <v>-4.331559161369242</v>
+        <v>-3.797619101887041</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>11.18539862003693</v>
       </c>
       <c r="E56">
-        <v>-12.18024314361257</v>
+        <v>-7.261038813138391</v>
       </c>
       <c r="F56">
-        <v>-2.239121968854322</v>
+        <v>-3.11214085976693</v>
       </c>
       <c r="G56">
-        <v>-4.630432508332824</v>
+        <v>-4.633175609556519</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>10.83401966859734</v>
       </c>
       <c r="E57">
-        <v>-10.48990417924346</v>
+        <v>-8.855600552245269</v>
       </c>
       <c r="F57">
-        <v>-1.801381155253758</v>
+        <v>-2.295332495706089</v>
       </c>
       <c r="G57">
-        <v>-3.849738025137261</v>
+        <v>-3.124105720930741</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.48653478289463</v>
       </c>
       <c r="E58">
-        <v>-10.12370007166519</v>
+        <v>-8.048789509142688</v>
       </c>
       <c r="F58">
-        <v>-2.135243039808459</v>
+        <v>-2.884946188935915</v>
       </c>
       <c r="G58">
-        <v>-4.42977924752966</v>
+        <v>-4.841273962078063</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.14483564110622</v>
       </c>
       <c r="E59">
-        <v>-9.526416992423503</v>
+        <v>-7.909629502886978</v>
       </c>
       <c r="F59">
-        <v>-2.242770098896252</v>
+        <v>-2.898612594347302</v>
       </c>
       <c r="G59">
-        <v>-4.624824900687733</v>
+        <v>-3.884676472302228</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>9.809075014747286</v>
       </c>
       <c r="E60">
-        <v>-8.858512361032203</v>
+        <v>-5.463895789298379</v>
       </c>
       <c r="F60">
-        <v>-2.018180643547041</v>
+        <v>-2.749260436724759</v>
       </c>
       <c r="G60">
-        <v>-4.366514014642006</v>
+        <v>-4.905917308020682</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>9.500787944777228</v>
       </c>
       <c r="E61">
-        <v>-8.513419999277682</v>
+        <v>-5.389719385052739</v>
       </c>
       <c r="F61">
-        <v>-2.050747907988104</v>
+        <v>-2.571412440445914</v>
       </c>
       <c r="G61">
-        <v>-5.652139277512719</v>
+        <v>-4.863596112346965</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.212083475630408</v>
       </c>
       <c r="E62">
-        <v>-8.914629210935253</v>
+        <v>-6.526293905393875</v>
       </c>
       <c r="F62">
-        <v>-2.312222078681768</v>
+        <v>-2.802062231714005</v>
       </c>
       <c r="G62">
-        <v>-5.065650454756011</v>
+        <v>-4.012762237096712</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>8.965205783364857</v>
       </c>
       <c r="E63">
-        <v>-7.329550096400436</v>
+        <v>-5.439695624201389</v>
       </c>
       <c r="F63">
-        <v>-2.263082495980298</v>
+        <v>-3.152741631280342</v>
       </c>
       <c r="G63">
-        <v>-4.950043175552095</v>
+        <v>-4.063913199986896</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.761200040308356</v>
       </c>
       <c r="E64">
-        <v>-7.908116992568416</v>
+        <v>-5.084916856544463</v>
       </c>
       <c r="F64">
-        <v>-2.489742041469105</v>
+        <v>-3.14498562728793</v>
       </c>
       <c r="G64">
-        <v>-4.677176790668673</v>
+        <v>-5.43869581507084</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.60156263392366</v>
       </c>
       <c r="E65">
-        <v>-6.400411384928655</v>
+        <v>-5.471571552741381</v>
       </c>
       <c r="F65">
-        <v>-2.593746882360194</v>
+        <v>-3.379062374501403</v>
       </c>
       <c r="G65">
-        <v>-5.56745751150657</v>
+        <v>-4.327480602970852</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>8.500202336586336</v>
       </c>
       <c r="E66">
-        <v>-6.487145247597566</v>
+        <v>-5.382736478132911</v>
       </c>
       <c r="F66">
-        <v>-2.374836713924577</v>
+        <v>-3.26216399498574</v>
       </c>
       <c r="G66">
-        <v>-4.47811492232184</v>
+        <v>-3.435621614562862</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>8.442390047975584</v>
       </c>
       <c r="E67">
-        <v>-7.00707746231423</v>
+        <v>-3.423419743130208</v>
       </c>
       <c r="F67">
-        <v>-2.881848094849445</v>
+        <v>-2.997090567926912</v>
       </c>
       <c r="G67">
-        <v>-5.602481270432082</v>
+        <v>-4.857132105874859</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>8.443749787741556</v>
       </c>
       <c r="E68">
-        <v>-6.727498534028677</v>
+        <v>-4.867821812616746</v>
       </c>
       <c r="F68">
-        <v>-2.823864033388285</v>
+        <v>-3.649469659266857</v>
       </c>
       <c r="G68">
-        <v>-5.403737680576516</v>
+        <v>-4.24713004942317</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>8.495670153438377</v>
       </c>
       <c r="E69">
-        <v>-7.270195387581901</v>
+        <v>-4.266888783324881</v>
       </c>
       <c r="F69">
-        <v>-2.788761136327254</v>
+        <v>-3.93944132535163</v>
       </c>
       <c r="G69">
-        <v>-5.041937066545904</v>
+        <v>-4.830055465566321</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>8.595580798621217</v>
       </c>
       <c r="E70">
-        <v>-6.017506265210088</v>
+        <v>-3.728679647513259</v>
       </c>
       <c r="F70">
-        <v>-3.135604366451226</v>
+        <v>-3.675999782076317</v>
       </c>
       <c r="G70">
-        <v>-5.057112716258335</v>
+        <v>-4.742227008084664</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>8.749700168060706</v>
       </c>
       <c r="E71">
-        <v>-6.880080937243123</v>
+        <v>-4.027518175753434</v>
       </c>
       <c r="F71">
-        <v>-3.12822278452488</v>
+        <v>-3.78836202169425</v>
       </c>
       <c r="G71">
-        <v>-5.27791267743649</v>
+        <v>-4.365703552916823</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>8.939814279320601</v>
       </c>
       <c r="E72">
-        <v>-6.170224522644763</v>
+        <v>-4.724699391604323</v>
       </c>
       <c r="F72">
-        <v>-3.465137202958897</v>
+        <v>-3.70251913610954</v>
       </c>
       <c r="G72">
-        <v>-4.883542658206829</v>
+        <v>-3.707109886391318</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>9.180040920575038</v>
       </c>
       <c r="E73">
-        <v>-6.455781036620441</v>
+        <v>-4.76739384454864</v>
       </c>
       <c r="F73">
-        <v>-3.406225370006602</v>
+        <v>-4.19857701486719</v>
       </c>
       <c r="G73">
-        <v>-4.545192934661569</v>
+        <v>-4.035681569689434</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>9.458310844972102</v>
       </c>
       <c r="E74">
-        <v>-6.218045208165762</v>
+        <v>-3.813307769768603</v>
       </c>
       <c r="F74">
-        <v>-3.311229024620958</v>
+        <v>-4.001288892379447</v>
       </c>
       <c r="G74">
-        <v>-4.750006784402108</v>
+        <v>-4.363472322256401</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>9.77494224544566</v>
       </c>
       <c r="E75">
-        <v>-7.007195202638429</v>
+        <v>-3.664714952154915</v>
       </c>
       <c r="F75">
-        <v>-3.875312434496503</v>
+        <v>-3.700137579826492</v>
       </c>
       <c r="G75">
-        <v>-4.490790281205975</v>
+        <v>-4.031901602452953</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>10.13327234786678</v>
       </c>
       <c r="E76">
-        <v>-7.096080090460983</v>
+        <v>-5.278540819690424</v>
       </c>
       <c r="F76">
-        <v>-3.736495453502765</v>
+        <v>-4.509479868485901</v>
       </c>
       <c r="G76">
-        <v>-4.067253483534411</v>
+        <v>-2.820248198418362</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>10.51298538385078</v>
       </c>
       <c r="E77">
-        <v>-8.148080830234868</v>
+        <v>-6.381985024191445</v>
       </c>
       <c r="F77">
-        <v>-3.867802455622723</v>
+        <v>-4.150580579181584</v>
       </c>
       <c r="G77">
-        <v>-3.829525700331081</v>
+        <v>-3.759947397163056</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>10.92276275352651</v>
       </c>
       <c r="E78">
-        <v>-7.322979280615306</v>
+        <v>-7.128019417637082</v>
       </c>
       <c r="F78">
-        <v>-3.505889565707022</v>
+        <v>-4.530637200320803</v>
       </c>
       <c r="G78">
-        <v>-3.094279416955388</v>
+        <v>-2.754062678342803</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>11.33951185063451</v>
       </c>
       <c r="E79">
-        <v>-8.818349325058174</v>
+        <v>-7.025580807109571</v>
       </c>
       <c r="F79">
-        <v>-4.235996855553853</v>
+        <v>-4.469840831527139</v>
       </c>
       <c r="G79">
-        <v>-3.468292737630253</v>
+        <v>-1.84396337928586</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>11.75583165692427</v>
       </c>
       <c r="E80">
-        <v>-9.259861955384011</v>
+        <v>-7.086977857705565</v>
       </c>
       <c r="F80">
-        <v>-4.283276753436037</v>
+        <v>-4.066166627366703</v>
       </c>
       <c r="G80">
-        <v>-2.95800372314853</v>
+        <v>-2.061866021827024</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>12.16049805094431</v>
       </c>
       <c r="E81">
-        <v>-10.18183209250165</v>
+        <v>-7.138231126524379</v>
       </c>
       <c r="F81">
-        <v>-4.271831201031556</v>
+        <v>-5.263531946478055</v>
       </c>
       <c r="G81">
-        <v>-2.541495302057296</v>
+        <v>-1.034436802247457</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>12.52462431185187</v>
       </c>
       <c r="E82">
-        <v>-10.67730149062888</v>
+        <v>-9.178036958539414</v>
       </c>
       <c r="F82">
-        <v>-4.533174489675578</v>
+        <v>-4.351826641119905</v>
       </c>
       <c r="G82">
-        <v>-2.711236174548931</v>
+        <v>-0.6334518403539562</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>12.84642794383611</v>
       </c>
       <c r="E83">
-        <v>-12.10113070269857</v>
+        <v>-10.65199184940001</v>
       </c>
       <c r="F83">
-        <v>-4.706027430515543</v>
+        <v>-4.806153026859322</v>
       </c>
       <c r="G83">
-        <v>-1.801737339037366</v>
+        <v>-0.2541820027408603</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>13.09541353488532</v>
       </c>
       <c r="E84">
-        <v>-12.55514644975958</v>
+        <v>-9.812942599836822</v>
       </c>
       <c r="F84">
-        <v>-4.774171418172038</v>
+        <v>-4.839282752766885</v>
       </c>
       <c r="G84">
-        <v>-1.623186386658622</v>
+        <v>-0.7073285437648539</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>13.26298343224911</v>
       </c>
       <c r="E85">
-        <v>-12.41620381025624</v>
+        <v>-13.09738592743803</v>
       </c>
       <c r="F85">
-        <v>-4.754313794792129</v>
+        <v>-5.086177657171278</v>
       </c>
       <c r="G85">
-        <v>-1.473897368147007</v>
+        <v>-0.7892376775532723</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>13.33607609357137</v>
       </c>
       <c r="E86">
-        <v>-13.78171986252916</v>
+        <v>-13.46477649520632</v>
       </c>
       <c r="F86">
-        <v>-5.158193434068458</v>
+        <v>-6.047507140161535</v>
       </c>
       <c r="G86">
-        <v>-1.22386500409576</v>
+        <v>0.6130218868694619</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>13.29519954725694</v>
       </c>
       <c r="E87">
-        <v>-15.30689632289051</v>
+        <v>-14.54988943692429</v>
       </c>
       <c r="F87">
-        <v>-5.1635910760651</v>
+        <v>-5.50401280208257</v>
       </c>
       <c r="G87">
-        <v>-1.212954942410606</v>
+        <v>-1.672975642601636</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>13.14515315984288</v>
       </c>
       <c r="E88">
-        <v>-17.16311781863459</v>
+        <v>-15.71107621349712</v>
       </c>
       <c r="F88">
-        <v>-5.413922048456305</v>
+        <v>-5.784134351380654</v>
       </c>
       <c r="G88">
-        <v>-0.1120493284503936</v>
+        <v>0.8911185389186393</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>12.86967377229957</v>
       </c>
       <c r="E89">
-        <v>-18.59395257999415</v>
+        <v>-17.60560859934609</v>
       </c>
       <c r="F89">
-        <v>-5.636070305069465</v>
+        <v>-5.704104119861388</v>
       </c>
       <c r="G89">
-        <v>-1.186508296641482</v>
+        <v>1.437074431751527</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>12.47618560497559</v>
       </c>
       <c r="E90">
-        <v>-20.66922089196325</v>
+        <v>-18.06810164974946</v>
       </c>
       <c r="F90">
-        <v>-6.108025177507859</v>
+        <v>-6.260945941901661</v>
       </c>
       <c r="G90">
-        <v>-0.8108609276300131</v>
+        <v>1.240919725706362</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.96555449751373</v>
       </c>
       <c r="E91">
-        <v>-21.79144920664809</v>
+        <v>-20.11206009242953</v>
       </c>
       <c r="F91">
-        <v>-6.656294225296559</v>
+        <v>-6.282558875808103</v>
       </c>
       <c r="G91">
-        <v>-0.613078735691364</v>
+        <v>0.3647351326878397</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.33793986664216</v>
       </c>
       <c r="E92">
-        <v>-23.40067414459181</v>
+        <v>-23.07547084067897</v>
       </c>
       <c r="F92">
-        <v>-6.25661358038502</v>
+        <v>-6.672958492338676</v>
       </c>
       <c r="G92">
-        <v>-1.727470170260894</v>
+        <v>-0.8451004746028187</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>10.61043500732947</v>
       </c>
       <c r="E93">
-        <v>-24.93809107019589</v>
+        <v>-26.47813903919844</v>
       </c>
       <c r="F93">
-        <v>-6.739313620588827</v>
+        <v>-6.720481930237284</v>
       </c>
       <c r="G93">
-        <v>-1.024228921976025</v>
+        <v>0.1186172659570105</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>9.782444702118472</v>
       </c>
       <c r="E94">
-        <v>-26.8650563868878</v>
+        <v>-25.583448429503</v>
       </c>
       <c r="F94">
-        <v>-6.871236099689065</v>
+        <v>-7.10262065284344</v>
       </c>
       <c r="G94">
-        <v>-1.172881383505108</v>
+        <v>-1.703277723703108</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>8.876734677713568</v>
       </c>
       <c r="E95">
-        <v>-28.75765058586149</v>
+        <v>-28.33359069436121</v>
       </c>
       <c r="F95">
-        <v>-7.275706779107292</v>
+        <v>-7.711563056866488</v>
       </c>
       <c r="G95">
-        <v>-2.561842156947413</v>
+        <v>-0.8627042282692395</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.897311220154022</v>
       </c>
       <c r="E96">
-        <v>-31.09286915552989</v>
+        <v>-31.38839963350746</v>
       </c>
       <c r="F96">
-        <v>-7.400228209647218</v>
+        <v>-7.083472526144027</v>
       </c>
       <c r="G96">
-        <v>-1.397595842003679</v>
+        <v>-2.057685745560291</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>6.866047838128853</v>
       </c>
       <c r="E97">
-        <v>-33.5847185841756</v>
+        <v>-32.00652954284346</v>
       </c>
       <c r="F97">
-        <v>-7.54430739456724</v>
+        <v>-7.806127822835274</v>
       </c>
       <c r="G97">
-        <v>-2.439085095965467</v>
+        <v>-1.383716274807228</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.788192445315445</v>
       </c>
       <c r="E98">
-        <v>-35.19402503465146</v>
+        <v>-33.58118863868663</v>
       </c>
       <c r="F98">
-        <v>-7.618274805065417</v>
+        <v>-8.248216736933134</v>
       </c>
       <c r="G98">
-        <v>-3.623852170541968</v>
+        <v>-2.804527865927063</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.700838328462806</v>
       </c>
       <c r="E99">
-        <v>-36.90372775387736</v>
+        <v>-36.42152678459261</v>
       </c>
       <c r="F99">
-        <v>-8.019866907758916</v>
+        <v>-8.135078731242478</v>
       </c>
       <c r="G99">
-        <v>-3.85807560911981</v>
+        <v>-3.639405160733736</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.589322350335626</v>
       </c>
       <c r="E100">
-        <v>-39.961715681777</v>
+        <v>-38.43766454720655</v>
       </c>
       <c r="F100">
-        <v>-7.861085858174008</v>
+        <v>-7.450161368320569</v>
       </c>
       <c r="G100">
-        <v>-4.684569382842102</v>
+        <v>-5.849685221499088</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.545837463660849</v>
       </c>
       <c r="E101">
-        <v>-41.9728698587455</v>
+        <v>-42.03283817579208</v>
       </c>
       <c r="F101">
-        <v>-8.080350567858023</v>
+        <v>-7.623783448294033</v>
       </c>
       <c r="G101">
-        <v>-5.233209314910614</v>
+        <v>-4.856584141874431</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.474979057417699</v>
       </c>
       <c r="E102">
-        <v>-44.96331106834673</v>
+        <v>-45.12017967220944</v>
       </c>
       <c r="F102">
-        <v>-8.037997385103989</v>
+        <v>-8.288510598323809</v>
       </c>
       <c r="G102">
-        <v>-5.819222360541203</v>
+        <v>-5.44714496058641</v>
       </c>
     </row>
   </sheetData>
